--- a/Dataset/EN/xlsx/ITAMed_2024_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2024_EN.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Bentall surgical procedure involves:</t>
+          <t>The Bentall surgical procedure involves</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A 35-year-old man, a heavy smoker, has complained for a few months of the onset of pain in the right lower limb during walking. The limb appears cold and the skin shows erythematous, painful areas. This is most likely:</t>
+          <t>A 35-year-old man, a heavy smoker, has complained for a few months of the onset of pain in the right lower limb during walking. The limb appears cold and the skin shows erythematous, painful areas. This is most likely</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A 60-year-old woman presents, after numerous episodes of biliary colic, with abdominal distension, subicterus, nausea associated with vomiting, and fever with chills. The most likely diagnosis among the following is:</t>
+          <t>A 60-year-old woman presents, after numerous episodes of biliary colic, with abdominal distension, subicterus, nausea associated with vomiting, and fever with chills. The most likely diagnosis among the following is</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sleeve gastrectomy:</t>
+          <t>Sleeve gastrectomy</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Necrotizing enterocolitis of the newborn:</t>
+          <t>Necrotizing enterocolitis of the newborn</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ulcers are:</t>
+          <t>Ulcers are</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The left internal mammary artery normally arises from:</t>
+          <t>The left internal mammary artery normally arises from</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>During a gynecological examination of a 35-year-old woman, in the absence of symptoms, ultrasound examination reveals an intramural uterine fibroid measuring 10 cm in diameter. The patient asks the physician what the future consequences might be. The gynecologist will mention all of the following conditions EXCEPT:</t>
+          <t>During a gynecological examination of a 35-year-old woman, in the absence of symptoms, ultrasound examination reveals an intramural uterine fibroid measuring 10 cm in diameter. The patient asks the physician what the future consequences might be. The gynecologist will mention all of the following conditions EXCEPT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A patient presents to the outpatient clinic to investigate certain menstrual cycle abnormalities. During history taking, the physician notes in the medical record the reported presence of dysmenorrhea, which means:</t>
+          <t>A patient presents to the outpatient clinic to investigate certain menstrual cycle abnormalities. During history taking, the physician notes in the medical record the reported presence of dysmenorrhea, which means</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The Amsler test is:</t>
+          <t>The Amsler test is</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A 72-year-old man presents with tearing, hyperemia and pain in the left eye and in the ipsilateral periorbital and frontal region. Slit lamp examination, following fluorescein staining, reveals the presence of a dendritic corneal lesion. This finding is indicative of:</t>
+          <t>A 72-year-old man presents with tearing, hyperemia and pain in the left eye and in the ipsilateral periorbital and frontal region. Slit lamp examination, following fluorescein staining, reveals the presence of a dendritic corneal lesion. This finding is indicative of</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>A 50-year-old woman undergoes a contrast-enhanced CT scan that reveals a fluid-containing mass in the lower pole of the right kidney, with thick septa and solid areas within it that take up contrast. The radiological findings are consistent with:</t>
+          <t>A 50-year-old woman undergoes a contrast-enhanced CT scan that reveals a fluid-containing mass in the lower pole of the right kidney, with thick septa and solid areas within it that take up contrast. The radiological findings are consistent with</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>In a 75-year-old woman who presented for evaluation for persistent polycythemia, after secondary causes of erythrocytosis had been excluded, the JAK2 V617F mutation was detected in a homozygous state. In light of the clinical and laboratory picture, the therapeutic strategy will be based on:</t>
+          <t>In a 75-year-old woman who presented for evaluation for persistent polycythemia, after secondary causes of erythrocytosis had been excluded, the JAK2 V617F mutation was detected in a homozygous state. In light of the clinical and laboratory picture, the therapeutic strategy will be based on</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A 78-year-old man, in fairly good general condition, with arterial hypertension and dyslipidemia, presents to the Emergency Department for acute urinary retention. On examination, a distended bladder is noted. The most likely cause among the following is:</t>
+          <t>A 78-year-old man, in fairly good general condition, with arterial hypertension and dyslipidemia, presents to the Emergency Department for acute urinary retention. On examination, a distended bladder is noted. The most likely cause among the following is</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>An 82-year-old patient presents to the Geriatrics Unit with a unilateral pleural effusion. The history reveals that the patient worked for several years in a factory where asbestos was used. Given the clinical picture, pleural mesothelioma is suspected. Confirmation of the clinical suspicion requires:</t>
+          <t>An 82-year-old patient presents to the Geriatrics Unit with a unilateral pleural effusion. The history reveals that the patient worked for several years in a factory where asbestos was used. Given the clinical picture, pleural mesothelioma is suspected. Confirmation of the clinical suspicion requires</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>When taking the medical history of a smoking patient, it emerges that he has smoked 15 cigarettes/day for 40 consecutive years. The calculation of the patient's pack-years (p-y), used to quantify his smoking habit, is:</t>
+          <t>When taking the medical history of a smoking patient, it emerges that he has smoked 15 cigarettes/day for 40 consecutive years. The calculation of the patient's pack-years (p-y), used to quantify his smoking habit, is</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>A young female patient with a known history of psychiatric disorders presents with repeated episodes of vomiting associated with sweating and accompanied by general malaise. First responders find two empty blister packs, each containing ten 1 g tablets of paracetamol, near the patient, who admits to having taken all of them approximately one hour earlier. Once transferred to the nearest Emergency Department, after performing electrocardiographic and multiparametric monitoring and gastric lavage, the treatment of choice to be administered is:</t>
+          <t>A young female patient with a known history of psychiatric disorders presents with repeated episodes of vomiting associated with sweating and accompanied by general malaise. First responders find two empty blister packs, each containing ten 1 g tablets of paracetamol, near the patient, who admits to having taken all of them approximately one hour earlier. Once transferred to the nearest Emergency Department, after performing electrocardiographic and multiparametric monitoring and gastric lavage, the treatment of choice to be administered is</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>A 70-year-old man presents to his General Practitioner complaining of unsteadiness of gait for several months. He also reports the recent onset of episodes of urinary incontinence. In addition, over the past few weeks, memory and attention deficits have appeared. In light of the reported symptoms, the most likely diagnosis is:</t>
+          <t>A 70-year-old man presents to his General Practitioner complaining of unsteadiness of gait for several months. He also reports the recent onset of episodes of urinary incontinence. In addition, over the past few weeks, memory and attention deficits have appeared. In light of the reported symptoms, the most likely diagnosis is</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Antineoplastic treatment with palbociclib is indicated in patients with:</t>
+          <t>Antineoplastic treatment with palbociclib is indicated in patients with</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>A female newborn delivered by spontaneous vaginal delivery at 36 weeks of gestation presents with macrocephaly (head circumference &gt; 97th percentile). While awaiting the results of other tests, a transfontanellar cranial ultrasound and a fundus oculi examination are performed, which reveal hydrocephalus with intracranial calcifications and chorioretinitis. The clinical picture is strongly suggestive of a diagnosis of:</t>
+          <t>A female newborn delivered by spontaneous vaginal delivery at 36 weeks of gestation presents with macrocephaly (head circumference &gt; 97th percentile). While awaiting the results of other tests, a transfontanellar cranial ultrasound and a fundus oculi examination are performed, which reveal hydrocephalus with intracranial calcifications and chorioretinitis. The clinical picture is strongly suggestive of a diagnosis of</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>The ASA (Anesthesiologic Risk Classification) of a 45-year-old patient with a negative past medical history, scheduled to undergo emergency surgery for a ruptured abdominal aortic aneurysm, is:</t>
+          <t>The ASA (Anesthesiologic Risk Classification) of a 45-year-old patient with a negative past medical history, scheduled to undergo emergency surgery for a ruptured abdominal aortic aneurysm, is</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>A 70-year-old patient, who underwent cholecystectomy under general anesthesia, is transferred to the recovery room. Transfer to the general ward is indicated when, in two consecutive assessments, the minimum Aldrete Score (in the absence of a 0 for any individual item) is:</t>
+          <t>A 70-year-old patient, who underwent cholecystectomy under general anesthesia, is transferred to the recovery room. Transfer to the general ward is indicated when, in two consecutive assessments, the minimum Aldrete Score (in the absence of a 0 for any individual item) is</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>The crude mortality rate in Italy is approximately 100/100,000, whereas in Algeria it is below 50/100,000. The explanation for this difference is:</t>
+          <t>The crude mortality rate in Italy is approximately 100/100,000, whereas in Algeria it is below 50/100,000. The explanation for this difference is</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Preventive measures related to occupational exposure to chemical substances are based on:</t>
+          <t>Preventive measures related to occupational exposure to chemical substances are based on</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>A body is found in a park, and on external examination the forensic pathologist notes a head wound of elongated shape characterized by irregular, contused, and abraded margins with tissue bridges between the margins, with the cranial vault intact. These wound characteristics are typically produced by:</t>
+          <t>A body is found in a park, and on external examination the forensic pathologist notes a head wound of elongated shape characterized by irregular, contused, and abraded margins with tissue bridges between the margins, with the cranial vault intact. These wound characteristics are typically produced by</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Skeletal scintigraphy for the study of bone metabolism uses 99mTc-labeled radiopharmaceuticals that contain:</t>
+          <t>Skeletal scintigraphy for the study of bone metabolism uses 99mTc-labeled radiopharmaceuticals that contain</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>The intercept in a regression line is:</t>
+          <t>The intercept in a regression line is</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2024_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2024_EN.xlsx
@@ -1232,7 +1232,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>General Surgery</t>
+          <t>Dermatology and Venereology; General Surgery</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; General Surgery</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; General Surgery</t>
+          <t>General Surgery; Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Urology; Oncology</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Nephrology; Hematology</t>
+          <t>Hematology; Nephrology</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Gastroenterology; Hematology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pediatrics</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Pulmonology and Thoracic Surgery</t>
+          <t>Pulmonology and Thoracic Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Urology; Oncology</t>
+          <t>Oncology; Urology</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Oncology; Pharmacology and Toxicology</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Pediatrics</t>
+          <t>Ophthalmology; Pediatrics</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Medical Genetics; Pediatrics</t>
+          <t>Medical Genetics; Endocrinology</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Gastroenterology; Pediatrics</t>
+          <t>Pediatrics; Gastroenterology</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Pediatrics</t>
+          <t>Pediatrics; Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Immunology and Rheumatology; Orthopedics and Traumatology</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Oncology</t>
+          <t>Otorhinolaryngology</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Oncology; Dermatology and Venereology</t>
+          <t>Dermatology and Venereology; Oncology</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>General Surgery; Orthopedics and Traumatology</t>
+          <t>Orthopedics and Traumatology; General Surgery</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Hematology; Gastroenterology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2024_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2024_EN.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/EN/xlsx/ITAMed_2024_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2024_EN.xlsx
@@ -8562,7 +8562,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Brain TC scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2024_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2024_EN.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -473,15 +473,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Question Type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Image Category</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Image Path</t>
         </is>
@@ -544,6 +549,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -602,6 +612,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -660,6 +675,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -718,6 +738,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -776,6 +801,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -834,6 +864,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -892,6 +927,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -950,6 +990,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1008,6 +1053,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1066,6 +1116,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1124,6 +1179,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1182,6 +1242,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1240,6 +1305,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1298,6 +1368,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1356,6 +1431,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1414,6 +1494,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1472,6 +1557,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1530,6 +1620,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1588,6 +1683,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1646,6 +1746,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1704,6 +1809,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1762,6 +1872,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1820,6 +1935,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1878,6 +1998,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1936,6 +2061,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1994,6 +2124,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2052,6 +2187,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2110,6 +2250,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2168,6 +2313,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2226,6 +2376,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2284,6 +2439,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2342,6 +2502,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2400,6 +2565,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2458,6 +2628,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2516,6 +2691,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2574,6 +2754,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2632,6 +2817,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2690,6 +2880,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2748,6 +2943,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2806,6 +3006,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2864,6 +3069,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2924,10 +3134,15 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>images/2024/ssm2023622.png</t>
         </is>
@@ -2992,10 +3207,15 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>images/2024/ssm2023623.png</t>
         </is>
@@ -3058,6 +3278,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3116,6 +3341,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3174,6 +3404,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3232,6 +3467,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3290,6 +3530,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3348,6 +3593,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3406,6 +3656,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3464,6 +3719,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3522,6 +3782,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3580,6 +3845,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3638,6 +3908,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3696,6 +3971,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3754,6 +4034,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3812,6 +4097,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3870,6 +4160,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3928,6 +4223,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3986,6 +4286,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4044,6 +4349,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4102,6 +4412,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4160,6 +4475,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4220,10 +4540,15 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
           <t>Spirometry report</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>images/2024/ssm2023644.png</t>
         </is>
@@ -4286,6 +4611,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4344,6 +4674,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4402,6 +4737,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4460,6 +4800,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4518,6 +4863,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4576,6 +4926,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4634,6 +4989,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4692,6 +5052,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4752,10 +5117,15 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>images/2024/ssm2023653.png</t>
         </is>
@@ -4818,6 +5188,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4876,6 +5251,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4934,6 +5314,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4992,6 +5377,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5050,6 +5440,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5108,6 +5503,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5166,6 +5566,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5224,6 +5629,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5282,6 +5692,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5340,6 +5755,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5398,6 +5818,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5456,6 +5881,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5514,6 +5944,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5572,6 +6007,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5630,6 +6070,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5688,6 +6133,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5746,6 +6196,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5804,6 +6259,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5862,6 +6322,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5920,6 +6385,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5978,6 +6448,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6036,6 +6511,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6094,6 +6574,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6152,6 +6637,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6210,6 +6700,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6268,6 +6763,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6326,6 +6826,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6384,6 +6889,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6442,6 +6952,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6500,6 +7015,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6558,6 +7078,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6616,6 +7141,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6674,6 +7204,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6732,6 +7267,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6790,6 +7330,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6848,6 +7393,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6906,6 +7456,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6964,6 +7519,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7022,6 +7582,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7080,6 +7645,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7138,6 +7708,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7196,6 +7771,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7254,6 +7834,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7312,6 +7897,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7370,6 +7960,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7428,6 +8023,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7488,10 +8088,15 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
           <t>Clinical study table</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr">
+      <c r="O121" t="inlineStr">
         <is>
           <t>images/2024/ssm2023700.png</t>
         </is>
@@ -7554,6 +8159,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7612,6 +8222,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7670,6 +8285,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7728,6 +8348,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7786,6 +8411,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7844,6 +8474,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7902,6 +8537,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7960,6 +8600,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8018,6 +8663,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8076,6 +8726,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8134,6 +8789,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8192,6 +8852,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8252,10 +8917,15 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr">
+      <c r="O134" t="inlineStr">
         <is>
           <t>images/2024/ssm2023713.png</t>
         </is>
@@ -8320,10 +8990,15 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr">
+      <c r="O135" t="inlineStr">
         <is>
           <t>images/2024/ssm2023714.png</t>
         </is>
@@ -8386,6 +9061,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8444,6 +9124,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8502,6 +9187,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8562,10 +9252,15 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr">
+      <c r="O139" t="inlineStr">
         <is>
           <t>images/2024/ssm2023718.png</t>
         </is>
@@ -8628,6 +9323,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8684,6 +9384,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
